--- a/tables/Datas/param.xlsx
+++ b/tables/Datas/param.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
   <si>
     <t>##column#var</t>
   </si>
@@ -77,6 +77,12 @@
   </si>
   <si>
     <t>新角色初始化地图id</t>
+  </si>
+  <si>
+    <t>GMCmdStatus</t>
+  </si>
+  <si>
+    <t>gm指令开启状态</t>
   </si>
 </sst>
 </file>
@@ -1119,8 +1125,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="4"/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="33.625" style="1" customWidth="1"/>
     <col min="2" max="3" width="22.125" style="1" customWidth="1"/>
@@ -1210,6 +1216,23 @@
       </c>
       <c r="E5" s="1">
         <v>10001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/tables/Datas/param.xlsx
+++ b/tables/Datas/param.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="20">
   <si>
     <t>##column#var</t>
   </si>
@@ -83,6 +83,12 @@
   </si>
   <si>
     <t>gm指令开启状态</t>
+  </si>
+  <si>
+    <t>DefaultHeadIcon</t>
+  </si>
+  <si>
+    <t>新角色默认头像</t>
   </si>
 </sst>
 </file>
@@ -1125,8 +1131,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="33.625" style="1" customWidth="1"/>
     <col min="2" max="3" width="22.125" style="1" customWidth="1"/>
@@ -1233,6 +1239,23 @@
       </c>
       <c r="E6" s="1">
         <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1001</v>
       </c>
     </row>
   </sheetData>
